--- a/docs/data/jp/xlsx/8877.xlsx
+++ b/docs/data/jp/xlsx/8877.xlsx
@@ -2076,7 +2076,7 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>Selling Of Real Estate Reportable Segments</t>
+          <t>부동산 판매 사업</t>
         </is>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -8276,7 +8276,7 @@
     <row r="97">
       <c r="A97" s="18" t="inlineStr">
         <is>
-          <t>Salaries And Bonuses SGA</t>
+          <t>급여 및 상여</t>
         </is>
       </c>
       <c r="C97" s="20" t="n">
@@ -9122,7 +9122,7 @@
     <row r="111">
       <c r="A111" s="18" t="inlineStr">
         <is>
-          <t>Cancellation Penalty Income NOI</t>
+          <t>해약 위약금 수입</t>
         </is>
       </c>
       <c r="C111" s="20" t="n">
@@ -9156,7 +9156,7 @@
     <row r="112">
       <c r="A112" s="18" t="inlineStr">
         <is>
-          <t>Gain On Guarantee Deposits Received NOI</t>
+          <t>보증금 공제 수입</t>
         </is>
       </c>
       <c r="C112" s="20" t="n">
@@ -11541,7 +11541,7 @@
     <row r="155">
       <c r="A155" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>부동산 판매 사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C155" s="20" t="n">
@@ -12027,7 +12027,7 @@
     <row r="166">
       <c r="A166" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>부동산 판매 사업 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C166" s="20" t="n">
@@ -12285,7 +12285,7 @@
     <row r="172">
       <c r="A172" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>부동산 판매 사업 · 계</t>
         </is>
       </c>
       <c r="C172" s="20" t="n">
@@ -12771,7 +12771,7 @@
     <row r="183">
       <c r="A183" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익</t>
+          <t>부동산 판매 사업 · 부문 이익</t>
         </is>
       </c>
       <c r="C183" s="20" t="n">
